--- a/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
@@ -1520,19 +1520,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1630,7 +1630,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1710,7 +1710,7 @@
         <v>206.6988</v>
       </c>
       <c r="P4" t="n">
-        <v>9.301446</v>
+        <v>9.301446000000002</v>
       </c>
       <c r="Q4" t="n">
         <v>0.04500000000000001</v>
@@ -1722,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>27.12358500000006</v>
+        <v>27.12358500000005</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>4.973799150320701e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1763,19 +1763,19 @@
         <v>287.5</v>
       </c>
       <c r="G5" t="n">
-        <v>195.4999999999999</v>
+        <v>195.5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>30.82226200000003</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.131628207280301e-14</v>
+        <v>3.552713678800501e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1843,19 +1843,19 @@
         <v>330.5826085</v>
       </c>
       <c r="G6" t="n">
-        <v>241.5</v>
+        <v>241.4999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8983223057065217</v>
+        <v>0.8983223057065218</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>37.41739150000001</v>
+        <v>37.41739149999995</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
         <v>1.952401500000029</v>
@@ -1864,16 +1864,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>344.1154000000001</v>
+        <v>344.1154</v>
       </c>
       <c r="O6" t="n">
-        <v>344.1154000000001</v>
+        <v>344.1154</v>
       </c>
       <c r="P6" t="n">
         <v>15.485193</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.045</v>
+        <v>0.04499999999999999</v>
       </c>
       <c r="R6" t="n">
         <v>45.36986301369863</v>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1920,19 +1920,19 @@
         <v>287.5</v>
       </c>
       <c r="F7" t="n">
-        <v>390.0000350000001</v>
+        <v>390.000035</v>
       </c>
       <c r="G7" t="n">
         <v>287.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8695652954292088</v>
+        <v>0.8695652954292087</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>58.49996499999986</v>
+        <v>58.49996499999992</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1944,16 +1944,16 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>408.3769999999999</v>
+        <v>408.377</v>
       </c>
       <c r="O7" t="n">
-        <v>408.3769999999999</v>
+        <v>408.377</v>
       </c>
       <c r="P7" t="n">
         <v>18.376965</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04500000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="R7" t="n">
         <v>55.2945205479452</v>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
   </sheetData>
@@ -8356,10 +8356,10 @@
         <v>16.6988</v>
       </c>
       <c r="M15" t="n">
-        <v>16.69879999999999</v>
+        <v>16.6988</v>
       </c>
       <c r="N15" t="n">
-        <v>16.69879999999999</v>
+        <v>16.6988</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -8731,10 +8731,10 @@
         <v>80.8169</v>
       </c>
       <c r="M20" t="n">
-        <v>80.81689999999999</v>
+        <v>80.8169</v>
       </c>
       <c r="N20" t="n">
-        <v>80.81689999999999</v>
+        <v>80.8169</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -10087,13 +10087,13 @@
         <v>2039</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8983223057065217</v>
+        <v>0.8983223057065218</v>
       </c>
       <c r="J2" t="n">
         <v>0.97</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07167769429347826</v>
+        <v>0.07167769429347814</v>
       </c>
     </row>
     <row r="3">
@@ -10126,13 +10126,13 @@
         <v>2040</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8695652954292088</v>
+        <v>0.8695652954292087</v>
       </c>
       <c r="J3" t="n">
         <v>0.97</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1004347045707912</v>
+        <v>0.1004347045707913</v>
       </c>
     </row>
     <row r="4">
@@ -10330,13 +10330,13 @@
         <v>2039</v>
       </c>
       <c r="I8" t="n">
-        <v>0.045</v>
+        <v>0.04499999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>0.025</v>
+        <v>0.02499999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -10369,7 +10369,7 @@
         <v>2040</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04500000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="J9" t="n">
         <v>0.02</v>
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.99</v>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -10744,7 +10744,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8983223057065217</v>
+        <v>0.8983223057065218</v>
       </c>
       <c r="G12" t="n">
         <v>0.97</v>
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8695652954292088</v>
+        <v>0.8695652954292087</v>
       </c>
       <c r="G13" t="n">
         <v>0.97</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.045</v>
+        <v>0.04499999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0.02</v>
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.04500000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="G37" t="n">
         <v>0.02</v>
@@ -22325,7 +22325,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95.91735649999988</v>
+        <v>95.91735649999987</v>
       </c>
     </row>
     <row r="9">
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="10">
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.095722698502202</v>
+        <v>8.0957226985022</v>
       </c>
     </row>
     <row r="11">
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.405830012604629</v>
+        <v>6.405830012604628</v>
       </c>
     </row>
     <row r="12">
@@ -22405,7 +22405,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8695652954292088</v>
+        <v>0.8695652954292087</v>
       </c>
     </row>
     <row r="13">
@@ -22425,7 +22425,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -22445,7 +22445,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.18211550000001</v>
+        <v>67.18211549999999</v>
       </c>
     </row>
     <row r="15">

--- a/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>6 / 2 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -735,7 +879,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -750,7 +894,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -768,7 +912,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -783,7 +927,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -800,7 +944,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -815,7 +959,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -832,7 +976,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -847,7 +991,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -864,7 +1008,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -879,7 +1023,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -896,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -911,7 +1055,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1072,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -943,7 +1087,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -960,7 +1104,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -975,7 +1119,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -992,7 +1136,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1007,7 +1151,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1168,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1039,7 +1183,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1200,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1071,7 +1215,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1232,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1103,7 +1247,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1264,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1135,7 +1279,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1296,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1167,7 +1311,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1328,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1199,7 +1343,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1360,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1231,7 +1375,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1392,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1263,7 +1407,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1424,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1295,7 +1439,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1456,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1327,7 +1471,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1488,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1359,7 +1503,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10224,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2039: total service level 0.8983 &lt; 0.97 (shortage 37.417 t) [guideline in this scenario]</t>
+          <t>2039: общий уровень сервиса 0.8983 &lt; 0.97 (дефицит 37.417 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10119,7 +10263,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2040: total service level 0.8696 &lt; 0.97 (shortage 58.500 t) [guideline in this scenario]</t>
+          <t>2040: общий уровень сервиса 0.8696 &lt; 0.97 (дефицит 58.500 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10158,7 +10302,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2038-01: physical stock 30.822 t &lt; 45-day reserve 35.445 t</t>
+          <t>2038-01: физический запас 30.822 т &lt; 45-дневного резерва 35.445 т</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10200,7 +10344,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2039-01: physical stock 1.952 t &lt; 45-day reserve 45.370 t</t>
+          <t>2039-01: физический запас 1.952 т &lt; 45-дневного резерва 45.370 т</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10242,7 +10386,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2040-01: physical stock 0.000 t &lt; 45-day reserve 55.295 t</t>
+          <t>2040-01: физический запас 0.000 т &lt; 45-дневного резерва 55.295 т</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10284,7 +10428,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2038: losses/throughput 0.0450 &gt; 0.02 (12.187 t of 270.817 t)</t>
+          <t>2038: потери/поступление 0.0450 &gt; 0.02 (12.187 т из 270.817 т)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -10323,7 +10467,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2039: losses/throughput 0.0450 &gt; 0.02 (15.485 t of 344.115 t)</t>
+          <t>2039: потери/поступление 0.0450 &gt; 0.02 (15.485 т из 344.115 т)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -10362,7 +10506,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2040: losses/throughput 0.0450 &gt; 0.02 (18.377 t of 408.377 t)</t>
+          <t>2040: потери/поступление 0.0450 &gt; 0.02 (18.377 т из 408.377 т)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -11756,7 +11900,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11769,7 +11913,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11949,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11818,7 +11962,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11998,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11867,7 +12011,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11903,7 +12047,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11916,7 +12060,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11952,7 +12096,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11965,7 +12109,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12145,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12014,7 +12158,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12893,7 +13037,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -12903,7 +13047,7 @@
         <v/>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -13226,7 +13370,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -13236,7 +13380,7 @@
         <v/>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -14162,7 +14306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14231,6 +14375,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14286,6 +14435,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14341,6 +14495,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14396,6 +14555,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14451,6 +14615,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14506,6 +14675,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14561,6 +14735,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14616,6 +14795,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14671,6 +14855,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14726,6 +14915,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14781,6 +14975,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14836,6 +15035,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14891,6 +15095,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14946,6 +15155,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15001,6 +15215,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15056,6 +15275,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15111,6 +15335,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15166,6 +15395,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15221,6 +15455,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15276,6 +15515,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15331,6 +15575,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15386,6 +15635,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15441,6 +15695,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15496,6 +15755,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15551,6 +15815,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15606,6 +15875,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15646,11 +15920,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2035-01</t>
+          <t>2037-01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -15659,7 +15933,12 @@
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -15716,6 +15995,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15756,11 +16040,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2035-02</t>
+          <t>2037-02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -15769,7 +16053,12 @@
         </is>
       </c>
       <c r="M29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -15826,6 +16115,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15866,11 +16160,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2035-03</t>
+          <t>2037-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -15879,7 +16173,12 @@
         </is>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -15936,6 +16235,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15976,11 +16280,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2035-04</t>
+          <t>2037-04</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -15989,7 +16293,12 @@
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -16046,6 +16355,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16086,11 +16400,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2035-05</t>
+          <t>2037-05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -16099,7 +16413,12 @@
         </is>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -16156,6 +16475,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16196,11 +16520,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2035-06</t>
+          <t>2037-06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -16209,7 +16533,12 @@
         </is>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -16266,6 +16595,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16306,11 +16640,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2035-07</t>
+          <t>2037-07</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -16319,7 +16653,12 @@
         </is>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -16376,6 +16715,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16416,11 +16760,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -16429,7 +16773,12 @@
         </is>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -16486,6 +16835,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16526,11 +16880,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2035-09</t>
+          <t>2037-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -16539,7 +16893,12 @@
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -16596,6 +16955,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16636,11 +17000,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2035-10</t>
+          <t>2037-10</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -16649,7 +17013,12 @@
         </is>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -16706,6 +17075,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16746,11 +17120,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2035-11</t>
+          <t>2037-11</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -16759,7 +17133,12 @@
         </is>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -16816,6 +17195,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16856,11 +17240,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2035-12</t>
+          <t>2037-12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -16869,7 +17253,12 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -16926,6 +17315,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16966,11 +17360,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2036-01</t>
+          <t>2038-01</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -16979,7 +17373,12 @@
         </is>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -17036,6 +17435,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17076,11 +17480,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2036-02</t>
+          <t>2038-02</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -17089,7 +17493,12 @@
         </is>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -17146,6 +17555,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17186,11 +17600,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2036-03</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -17199,7 +17613,12 @@
         </is>
       </c>
       <c r="M55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -17256,6 +17675,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17296,11 +17720,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2036-04</t>
+          <t>2038-04</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -17309,7 +17733,12 @@
         </is>
       </c>
       <c r="M57" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -17366,6 +17795,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17406,11 +17840,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2036-05</t>
+          <t>2038-05</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -17419,7 +17853,12 @@
         </is>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -17476,6 +17915,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17516,11 +17960,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2036-06</t>
+          <t>2038-06</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17529,7 +17973,12 @@
         </is>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -17586,6 +18035,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17626,11 +18080,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2036-07</t>
+          <t>2038-07</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -17639,7 +18093,12 @@
         </is>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -17696,6 +18155,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17736,11 +18200,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -17749,7 +18213,12 @@
         </is>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -17806,6 +18275,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17846,11 +18320,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2036-09</t>
+          <t>2038-09</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -17859,7 +18333,12 @@
         </is>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -17916,6 +18395,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17956,11 +18440,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2036-10</t>
+          <t>2038-10</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -17969,7 +18453,12 @@
         </is>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -18026,6 +18515,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18066,11 +18560,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2036-11</t>
+          <t>2038-11</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -18079,7 +18573,12 @@
         </is>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -18136,6 +18635,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18176,11 +18680,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2036-12</t>
+          <t>2038-12</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -18189,7 +18693,12 @@
         </is>
       </c>
       <c r="M73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -18246,6 +18755,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18301,6 +18815,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18341,20 +18860,25 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>2039-01</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>2037-01</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
       <c r="M76" t="b">
         <v>1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -18411,6 +18935,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18466,6 +18995,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18506,11 +19040,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J79" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2037-02</t>
+          <t>2039-02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -18520,6 +19054,11 @@
       </c>
       <c r="M79" t="b">
         <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -18576,6 +19115,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18631,6 +19175,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18671,11 +19220,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2037-03</t>
+          <t>2039-03</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -18685,6 +19234,11 @@
       </c>
       <c r="M82" t="b">
         <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -18741,6 +19295,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18796,6 +19355,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18836,11 +19400,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2037-04</t>
+          <t>2039-04</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -18850,6 +19414,11 @@
       </c>
       <c r="M85" t="b">
         <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -18906,6 +19475,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18961,6 +19535,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19001,11 +19580,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2037-05</t>
+          <t>2039-05</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -19015,6 +19594,11 @@
       </c>
       <c r="M88" t="b">
         <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -19071,6 +19655,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19126,6 +19715,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19166,11 +19760,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2037-06</t>
+          <t>2039-06</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -19180,6 +19774,11 @@
       </c>
       <c r="M91" t="b">
         <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -19236,6 +19835,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19291,6 +19895,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19331,11 +19940,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2037-07</t>
+          <t>2039-07</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -19345,6 +19954,11 @@
       </c>
       <c r="M94" t="b">
         <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -19401,6 +20015,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19456,6 +20075,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19496,11 +20120,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2039-08</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -19510,6 +20134,11 @@
       </c>
       <c r="M97" t="b">
         <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -19566,6 +20195,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19621,6 +20255,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19661,11 +20300,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2037-09</t>
+          <t>2039-09</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -19675,6 +20314,11 @@
       </c>
       <c r="M100" t="b">
         <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -19731,6 +20375,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19786,6 +20435,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19826,11 +20480,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2037-10</t>
+          <t>2039-10</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -19840,6 +20494,11 @@
       </c>
       <c r="M103" t="b">
         <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -19896,6 +20555,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19951,6 +20615,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19991,11 +20660,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2037-11</t>
+          <t>2039-11</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -20005,6 +20674,11 @@
       </c>
       <c r="M106" t="b">
         <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -20061,6 +20735,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20116,6 +20795,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20156,11 +20840,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J109" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2037-12</t>
+          <t>2039-12</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -20170,6 +20854,11 @@
       </c>
       <c r="M109" t="b">
         <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -20226,6 +20915,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20281,6 +20975,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20321,11 +21020,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2038-01</t>
+          <t>2040-01</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -20335,6 +21034,11 @@
       </c>
       <c r="M112" t="b">
         <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -20391,6 +21095,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20446,6 +21155,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20486,11 +21200,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J115" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2038-02</t>
+          <t>2040-02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -20500,6 +21214,11 @@
       </c>
       <c r="M115" t="b">
         <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -20556,6 +21275,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20611,6 +21335,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20651,11 +21380,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2038-03</t>
+          <t>2040-03</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -20665,6 +21394,11 @@
       </c>
       <c r="M118" t="b">
         <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -20721,6 +21455,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20776,6 +21515,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20816,11 +21560,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J121" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2038-04</t>
+          <t>2040-04</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -20830,6 +21574,11 @@
       </c>
       <c r="M121" t="b">
         <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -20886,6 +21635,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20941,6 +21695,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20981,11 +21740,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J124" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2038-05</t>
+          <t>2040-05</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -20995,6 +21754,11 @@
       </c>
       <c r="M124" t="b">
         <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -21051,6 +21815,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21106,6 +21875,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21146,11 +21920,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J127" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2038-06</t>
+          <t>2040-06</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -21160,6 +21934,11 @@
       </c>
       <c r="M127" t="b">
         <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -21216,6 +21995,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21271,6 +22055,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21311,11 +22100,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2038-07</t>
+          <t>2040-07</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -21325,6 +22114,11 @@
       </c>
       <c r="M130" t="b">
         <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -21381,6 +22175,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21436,6 +22235,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21476,11 +22280,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2040-08</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -21490,6 +22294,11 @@
       </c>
       <c r="M133" t="b">
         <v>1</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -21546,6 +22355,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21601,6 +22415,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21641,11 +22460,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J136" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2038-09</t>
+          <t>2040-09</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -21655,6 +22474,11 @@
       </c>
       <c r="M136" t="b">
         <v>1</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -21711,6 +22535,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21766,6 +22595,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21806,11 +22640,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J139" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2038-10</t>
+          <t>2040-10</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -21820,6 +22654,11 @@
       </c>
       <c r="M139" t="b">
         <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -21876,6 +22715,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21931,6 +22775,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21971,11 +22820,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J142" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2038-11</t>
+          <t>2040-11</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -21985,6 +22834,11 @@
       </c>
       <c r="M142" t="b">
         <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -22041,6 +22895,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -22096,6 +22955,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22136,11 +23000,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J145" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2038-12</t>
+          <t>2040-12</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -22150,6 +23014,11 @@
       </c>
       <c r="M145" t="b">
         <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22745,7 +23614,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11889,18 +11922,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11913,7 +11946,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11938,18 +11971,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11962,7 +11995,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11987,18 +12020,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12011,7 +12044,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12036,18 +12069,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12060,7 +12093,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12085,18 +12118,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12109,7 +12142,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12134,18 +12167,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12158,7 +12191,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12351,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -12342,7 +12375,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12586,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -12577,7 +12610,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12821,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -12812,7 +12845,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13154,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -13145,7 +13178,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13454,7 +13487,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -13478,7 +13511,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13918,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -13909,7 +13942,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,6 +1536,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
@@ -7499,7 +7499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7608,6 +7608,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7683,6 +7688,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7758,6 +7766,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7833,6 +7844,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7908,6 +7922,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7983,6 +8000,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8058,6 +8078,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8133,6 +8156,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8208,6 +8234,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8283,6 +8312,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8358,6 +8390,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8433,6 +8468,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8508,6 +8546,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8583,6 +8624,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8658,6 +8702,9 @@
       <c r="U15" t="n">
         <v>5.0097</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8733,6 +8780,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8808,6 +8858,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8883,6 +8936,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8958,6 +9014,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9033,6 +9092,9 @@
       <c r="U20" t="n">
         <v>24.2451</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9108,6 +9170,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9183,6 +9248,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9258,6 +9326,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9333,6 +9404,9 @@
       <c r="U24" t="n">
         <v>3.6174</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9408,6 +9482,9 @@
       <c r="U25" t="n">
         <v>39</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9483,6 +9560,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9558,6 +9638,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9633,6 +9716,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9708,6 +9794,9 @@
       <c r="U29" t="n">
         <v>13.25655</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9783,6 +9872,9 @@
       <c r="U30" t="n">
         <v>39</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9858,6 +9950,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9931,6 +10026,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9945,7 +10043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10009,6 +10107,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10051,6 +10154,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10093,6 +10199,9 @@
       <c r="L3" t="n">
         <v>360</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10135,6 +10244,9 @@
       <c r="L4" t="n">
         <v>360</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10177,6 +10289,9 @@
       <c r="L5" t="n">
         <v>360</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10219,6 +10334,9 @@
       <c r="L6" t="n">
         <v>360</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10260,6 +10378,9 @@
       </c>
       <c r="L7" t="n">
         <v>360</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23164,7 +23285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23602,11 +23723,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23622,11 +23743,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23642,11 +23763,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -23662,11 +23783,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -23682,11 +23803,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -23702,10 +23823,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23722,11 +23843,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>78</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23742,10 +23863,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>70</v>
       </c>
     </row>

--- a/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2_earth_new_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -831,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1355,7 +1357,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1375,24 +1377,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1402,29 +1404,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1434,29 +1436,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1466,176 +1468,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2372,6 +2517,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2444,6 +2599,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2515,6 +2676,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2586,6 +2753,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2657,6 +2830,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2728,6 +2907,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2799,6 +2984,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2870,6 +3061,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2941,6 +3138,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3012,6 +3215,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3083,6 +3292,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3154,6 +3369,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3225,6 +3446,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3296,6 +3523,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3367,6 +3600,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3438,6 +3677,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3509,6 +3754,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3580,6 +3831,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3651,6 +3908,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3722,6 +3985,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3793,6 +4062,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3864,6 +4139,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3935,6 +4216,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4006,6 +4293,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4077,6 +4370,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4148,6 +4447,12 @@
         <v>1.423987865000004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.87468750000008</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4219,6 +4524,12 @@
         <v>1.460974635000005</v>
       </c>
       <c r="U27" t="n">
+        <v>40.49113366666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4290,6 +4601,12 @@
         <v>1.497961405000004</v>
       </c>
       <c r="U28" t="n">
+        <v>41.1075798333334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4361,6 +4678,12 @@
         <v>1.534948175000004</v>
       </c>
       <c r="U29" t="n">
+        <v>41.72402600000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4432,6 +4755,12 @@
         <v>1.571934945000004</v>
       </c>
       <c r="U30" t="n">
+        <v>42.34047216666673</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4503,6 +4832,12 @@
         <v>1.608921715000003</v>
       </c>
       <c r="U31" t="n">
+        <v>42.95691833333339</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4574,6 +4909,12 @@
         <v>1.645908485000003</v>
       </c>
       <c r="U32" t="n">
+        <v>43.57336450000005</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4645,6 +4986,12 @@
         <v>1.682895255000003</v>
       </c>
       <c r="U33" t="n">
+        <v>44.18981066666672</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4716,6 +5063,12 @@
         <v>1.719882025000002</v>
       </c>
       <c r="U34" t="n">
+        <v>44.80625683333338</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4787,6 +5140,12 @@
         <v>1.756868795000002</v>
       </c>
       <c r="U35" t="n">
+        <v>45.42270300000004</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4858,6 +5217,12 @@
         <v>1.793855565000002</v>
       </c>
       <c r="U36" t="n">
+        <v>46.0391491666667</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4929,6 +5294,12 @@
         <v>1.830842335000002</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65559533333337</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5000,6 +5371,12 @@
         <v>1.777161068750002</v>
       </c>
       <c r="U38" t="n">
+        <v>52.37477362500003</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5071,6 +5448,12 @@
         <v>1.632811766250002</v>
       </c>
       <c r="U39" t="n">
+        <v>49.9689519166667</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5142,6 +5525,12 @@
         <v>1.488462463750002</v>
       </c>
       <c r="U40" t="n">
+        <v>47.56313020833336</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5213,6 +5602,12 @@
         <v>1.344113161250002</v>
       </c>
       <c r="U41" t="n">
+        <v>45.15730850000003</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5284,6 +5679,12 @@
         <v>1.199763858750002</v>
       </c>
       <c r="U42" t="n">
+        <v>42.75148679166669</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5355,6 +5756,12 @@
         <v>1.055414556250002</v>
       </c>
       <c r="U43" t="n">
+        <v>40.34566508333336</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5426,6 +5833,12 @@
         <v>0.9110652537500016</v>
       </c>
       <c r="U44" t="n">
+        <v>37.93984337500002</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5497,6 +5910,12 @@
         <v>0.7667159512500015</v>
       </c>
       <c r="U45" t="n">
+        <v>35.53402166666669</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5568,6 +5987,12 @@
         <v>0.6223666487500014</v>
       </c>
       <c r="U46" t="n">
+        <v>33.12819995833335</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5639,6 +6064,12 @@
         <v>0.4780173462500014</v>
       </c>
       <c r="U47" t="n">
+        <v>30.72237825000002</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5710,6 +6141,12 @@
         <v>0.3336680437500015</v>
       </c>
       <c r="U48" t="n">
+        <v>28.31655654166669</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5781,6 +6218,12 @@
         <v>0.1893187412500017</v>
       </c>
       <c r="U49" t="n">
+        <v>25.91073483333336</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5852,6 +6295,12 @@
         <v>0.05857204500000087</v>
       </c>
       <c r="U50" t="n">
+        <v>29.33825208333336</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5923,6 +6372,12 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5994,6 +6449,12 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6065,6 +6526,12 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6136,6 +6603,12 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6207,6 +6680,12 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6278,6 +6757,12 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6349,6 +6834,12 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6420,6 +6911,12 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6491,6 +6988,12 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6562,6 +7065,12 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6633,6 +7142,12 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
+        <v>27.38585058333333</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6704,6 +7219,12 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6775,6 +7296,12 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6846,6 +7373,12 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6917,6 +7450,12 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6988,6 +7527,12 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7059,6 +7604,12 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7130,6 +7681,12 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7201,6 +7758,12 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7272,6 +7835,12 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7343,6 +7912,12 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7414,6 +7989,12 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7485,6 +8066,12 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
+        <v>32.50000291666667</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10134,7 +10721,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10143,13 +10730,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10786,7 +11373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12612,7 +13199,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12620,14 +13207,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12644,7 +13231,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12661,7 +13248,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12669,14 +13256,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>109.876</v>
       </c>
       <c r="G40" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12710,7 +13297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12718,18 +13305,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -12739,7 +13327,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12754,7 +13346,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12762,7 +13354,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -12798,27 +13390,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -12828,11 +13419,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12847,7 +13434,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12855,14 +13442,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G44" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12879,7 +13466,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12896,7 +13483,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12904,14 +13491,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G45" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12928,7 +13515,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12945,7 +13532,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12953,170 +13540,170 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G46" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <f>=</f>
         <v/>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D49" t="n">
         <v>2036</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>30.82226200000003</v>
-      </c>
-      <c r="G48" t="n">
-        <v>70</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2037-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>190</v>
-      </c>
-      <c r="G49" t="n">
-        <v>190</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13131,7 +13718,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -13139,14 +13726,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>190</v>
+        <v>30.82226200000003</v>
       </c>
       <c r="G50" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -13163,7 +13750,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13767,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -13188,14 +13775,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>16.699</v>
+        <v>46.65559533333337</v>
       </c>
       <c r="G51" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -13212,7 +13799,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13816,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -13237,14 +13824,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>16.6988</v>
+        <v>190</v>
       </c>
       <c r="G52" t="n">
-        <v>16.699</v>
+        <v>190</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -13261,7 +13848,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13865,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -13286,219 +13873,219 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>190</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>16.699</v>
+      </c>
+      <c r="G54" t="n">
+        <v>130</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>16.6988</v>
+      </c>
+      <c r="G55" t="n">
+        <v>16.699</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56">
         <f>=</f>
         <v/>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>2037</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>28.4164402916667</v>
-      </c>
-      <c r="G55" t="n">
-        <v>70</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2038-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>190</v>
-      </c>
-      <c r="G56" t="n">
-        <v>190</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>190</v>
-      </c>
-      <c r="G57" t="n">
-        <v>190</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13513,7 +14100,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13521,14 +14108,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>80.81699999999999</v>
+        <v>28.4164402916667</v>
       </c>
       <c r="G58" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -13545,7 +14132,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13562,7 +14149,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13570,14 +14157,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>80.8169</v>
+        <v>52.37477362500003</v>
       </c>
       <c r="G59" t="n">
-        <v>80.81699999999999</v>
+        <v>70</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -13594,7 +14181,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-01, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13611,7 +14198,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -13619,268 +14206,268 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>190</v>
+      </c>
+      <c r="G60" t="n">
+        <v>190</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>190</v>
+      </c>
+      <c r="G61" t="n">
+        <v>190</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>80.81699999999999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>130</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>80.8169</v>
+      </c>
+      <c r="G63" t="n">
+        <v>80.81699999999999</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <f>=</f>
         <v/>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D65" t="n">
         <v>2038</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65">
         <f>=</f>
         <v/>
       </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>70</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2039-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>190</v>
-      </c>
-      <c r="G63" t="n">
-        <v>190</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>190</v>
-      </c>
-      <c r="G64" t="n">
-        <v>190</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>24.116</v>
-      </c>
-      <c r="G65" t="n">
-        <v>110</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13895,7 +14482,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13903,14 +14490,14 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>24.1154</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>24.116</v>
+        <v>70</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -13927,7 +14514,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13944,7 +14531,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -13952,14 +14539,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>130</v>
+        <v>29.33825208333336</v>
       </c>
       <c r="G67" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -13976,7 +14563,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-01, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13993,7 +14580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -14001,14 +14588,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="G68" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -14025,7 +14612,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14042,7 +14629,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -14050,317 +14637,317 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>190</v>
+      </c>
+      <c r="G69" t="n">
+        <v>190</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>24.116</v>
+      </c>
+      <c r="G70" t="n">
+        <v>110</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>24.1154</v>
+      </c>
+      <c r="G71" t="n">
+        <v>24.116</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>130</v>
+      </c>
+      <c r="G72" t="n">
+        <v>130</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>130</v>
+      </c>
+      <c r="G73" t="n">
+        <v>130</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74">
         <f>=</f>
         <v/>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D75" t="n">
         <v>2039</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75">
         <f>=</f>
         <v/>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>70</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>190</v>
-      </c>
-      <c r="G72" t="n">
-        <v>190</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>190</v>
-      </c>
-      <c r="G73" t="n">
-        <v>190</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>88.377</v>
-      </c>
-      <c r="G74" t="n">
-        <v>110</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>88.377</v>
-      </c>
-      <c r="G75" t="n">
-        <v>88.377</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14375,7 +14962,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -14383,14 +14970,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -14407,7 +14994,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14424,7 +15011,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -14432,14 +15019,14 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>130</v>
+        <v>32.50000291666667</v>
       </c>
       <c r="G77" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -14456,7 +15043,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-01, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14473,7 +15060,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -14481,72 +15068,366 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>190</v>
+      </c>
+      <c r="G78" t="n">
+        <v>190</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>190</v>
+      </c>
+      <c r="G79" t="n">
+        <v>190</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>88.377</v>
+      </c>
+      <c r="G80" t="n">
+        <v>110</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>88.377</v>
+      </c>
+      <c r="G81" t="n">
+        <v>88.377</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>130</v>
+      </c>
+      <c r="G82" t="n">
+        <v>130</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>130</v>
+      </c>
+      <c r="G83" t="n">
+        <v>130</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84">
         <f>=</f>
         <v/>
       </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D85" t="n">
         <v>2040</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85">
         <f>=</f>
         <v/>
       </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23285,7 +24166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23327,7 +24208,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11642.318299305</v>
+        <v>11642.688165075</v>
       </c>
     </row>
     <row r="3">
@@ -23347,7 +24228,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9212.112958338103</v>
+        <v>9212.482824108103</v>
       </c>
     </row>
     <row r="4">
@@ -23487,7 +24368,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.0957226985022</v>
+        <v>8.095979892184131</v>
       </c>
     </row>
     <row r="11">
@@ -23507,7 +24388,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.405830012604628</v>
+        <v>6.406087206286557</v>
       </c>
     </row>
     <row r="12">
@@ -23667,7 +24548,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56.68530430500009</v>
+        <v>57.0551700750001</v>
       </c>
     </row>
     <row r="20">
@@ -23783,11 +24664,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23803,11 +24684,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23823,11 +24704,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -23843,11 +24724,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -23863,11 +24744,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23883,11 +24764,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>70</v>
+      <c r="D32" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
